--- a/backend/public/excel/purchase.xlsx
+++ b/backend/public/excel/purchase.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>No</t>
   </si>
@@ -89,6 +89,21 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>PUR-1706941593676</t>
+  </si>
+  <si>
+    <t>10.000</t>
+  </si>
+  <si>
+    <t>1.100</t>
+  </si>
+  <si>
+    <t>11.100</t>
+  </si>
+  <si>
+    <t>Es Campur</t>
   </si>
 </sst>
 </file>
@@ -478,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -620,6 +635,38 @@
         <v>15</v>
       </c>
     </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>45308</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
